--- a/EstablecimientoSalud/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,12 +493,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26847</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>211105</t>
+          <t>211101</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,27 +513,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>JULIACA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-15.4791385</t>
+          <t>-15.4955005</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-70.1329288</t>
+          <t>-70.1316031</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>"AP CENTROS MEDICOS CUYO CUYO E.I.R.L.</t>
+          <t>POLICLINICO JULIACA - ESSALUD - RED ASISTENCIAL JULIACA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>URBANIZACION SAN JOSE II-E MANZANA MZA - H-5 LOTE LOTE-4 URBANIZACI? SAN JOSE II-E.H5 LOTE -4 DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JR. MARIANO NAAEZ 135 - JULIACA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-15.49386716</t>
+          <t>-15.4996879</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-70.13090827</t>
+          <t>-70.129653</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CLINICA PERUANO BRASILERO EIRL</t>
+          <t>POLICLINICO DE SALUD PNP - JULIACA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JR. SAN MARTIN 283- ESQUINA 8 DE NOVIEMBRE DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>Jr.NUEVA ZELANDA S/N CUADRA SEIS - LA CAPILLA NUMERO S/N DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>29844</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -642,27 +642,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-15.49833612</t>
+          <t>-15.4996879</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-70.13412692</t>
+          <t>-70.129653</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CENTRO UROLAGICO Y ESPECIALIDADES MEDICO QUIRARGICO</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO SAN MIGUEL ARCANGEL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LORETO NUMERO 506 URBANIZACION LA RINCONADA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>AEROPUERTO NUMERO 266 URBANIZACION SAN JOSE II ETAPA DISTRITO SAN MIGUEL PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>29841</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-15.4955005</t>
+          <t>-15.47996082</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-70.1316031</t>
+          <t>-70.14428713</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>POLICLINICO JULIACA - ESSALUD - RED ASISTENCIAL JULIACA</t>
+          <t>Centro de Salud Mental Comunitario Divino NiA±o Jesus</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>JR. MARIANO NAAEZ 135 - JULIACA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>PASAJE Las Violetas MANZANA A1 LOTE 05 URBANIZACION Guardia Civil DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27604</t>
+          <t>27818</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -766,27 +766,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-15.4996879</t>
+          <t>-15.53120166</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-70.129653</t>
+          <t>-70.13198252</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>POLICLINICO JULIACA DE VIRGEN DE COPACABANA</t>
+          <t>centro de salud mental comunitario san roman juliaca</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jr Almagro 109 3 4 CERRO COLORADO DANIEL ALCIDEZ CARRION CON VAA AUXILIAR, AL FRENTE DEL COLEGIO APLICACION UANCV JULIACA SAN ROMAN PUNO</t>
+          <t>URBANIZACION municipal taparachi III etapa sector pentagono hospital materno infantil JULIACA SAN ROMAN PUNO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -838,12 +838,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>POLICLINICO DE SALUD PNP - JULIACA</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO "SAN ISIDRO LABRADOR"</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jr.NUEVA ZELANDA S/N CUADRA SEIS - LA CAPILLA NUMERO S/N DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JUAN VELASCO ALVARADO CON ATAHUALLPA NUMERO S/N URBANIZACION SAN ISIDRO DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,22 +890,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-15.4935904</t>
+          <t>-15.516739</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-70.1244609</t>
+          <t>-70.12568175</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO FISIOLUZ E.I.R.L.</t>
+          <t>TAPARACHI</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AVENIDA TUPAC AMARU NUMERO 728 DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JR. CUBA MZ B-4 LOTE 12-13-14 JULIACA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26376</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-15.4663774</t>
+          <t>-15.43903137</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-70.1591366</t>
+          <t>-70.23655403</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CLINICA SAN PABLO - JULIACA</t>
+          <t>RANCHO PUCACHUPA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LORETO 439 Al frente de la escuela de post grado de la UANCV JULIACA SAN ROMAN PUNO</t>
+          <t>OTROS COMUNIDAD CAMPAESINA RANCHO PUCACHUPA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26979</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,27 +1014,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-15.4996879</t>
+          <t>-15.47607025</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-70.129653</t>
+          <t>-70.10929357</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Centro de AtenciA³n Integral "Sumaq kausay"</t>
+          <t>GUADALUPE</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CALLE 4 MANZANA Q LOTE 7;24 URBANIZACI? San Jorge DISTRITO SAN MIGUEL PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JR. ESCURI S/N MANZANA B LOTE 1 -2 URBANIZACION ANEXO TAMBOPATA NUMERO S/N DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1076,27 +1076,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-15.4996879</t>
+          <t>-15.43264619</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-70.129653</t>
+          <t>-70.18573532</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO SAN MIGUEL ARCANGEL</t>
+          <t>UNOCOLLA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AEROPUERTO NUMERO 266 URBANIZACION SAN JOSE II ETAPA DISTRITO SAN MIGUEL PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>OTROS COMUNIDAD UNOCOLLA SALIDA LAMPA KM8 DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29841</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-15.47996082</t>
+          <t>-15.50102712</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-70.14428713</t>
+          <t>-70.11093011</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Centro de Salud Mental Comunitario Divino NiA±o Jesus</t>
+          <t>9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PASAJE Las Violetas MANZANA A1 LOTE 05 URBANIZACION Guardia Civil DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JR. ALFONSO UGARTE 151 JULIACA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26980</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-15.49691775</t>
+          <t>-15.49997221</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-70.13162062</t>
+          <t>-70.13106384</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CLINICA MATERNIDAD JULIACA</t>
+          <t>ENFERMERIA BING Nº 4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LORETO NUMERO 219 DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JR. 7 DE JUNIO S/N - LA RINCONADA NUMERO S/N DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>32921</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1262,27 +1262,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-15.4928902</t>
+          <t>-15.4996879</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-70.1256722</t>
+          <t>-70.129653</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>POLICLINICO SAN FRANCISCO</t>
+          <t>ESTABLECIMIENTO PENAL JULIACA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AVENIDA AV RAUL PORRAS BARRENECHEA NUMERO 226 URBANIZACION ZARUMILLA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JIRON JOSE SANTOS CHOCANO S/N NUMERO S/N DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1324,27 +1324,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-15.49709288</t>
+          <t>-15.48032349</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-70.13211795</t>
+          <t>-70.13931455</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO MEDICA SUR</t>
+          <t>JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>JR. LORETO Nº 262 -JULIACA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JR. ANCASH S/N NUMERO S/N DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27818</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-15.53120166</t>
+          <t>-15.4955688</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-70.13198252</t>
+          <t>-70.1266406</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>centro de salud mental comunitario san roman juliaca</t>
+          <t>ENFERMERIA GAC Nº 4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>URBANIZACION municipal taparachi III etapa sector pentagono hospital materno infantil JULIACA SAN ROMAN PUNO</t>
+          <t>JR. RAMON CASTLLA S/N BARRIO ZARUMILLA-JULIACA NUMERO S/N DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26065</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,27 +1448,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-15.49748576</t>
+          <t>-15.4753026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-70.12629219</t>
+          <t>-70.26047882</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO JOVE ANDINA S.R.L.</t>
+          <t>ISLA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>RAMON CASTILLA NUMERO 137 URBANIZACION SARUMILLA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>OTROS KM 15 CENTRO POBLADO ISLA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28341</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,32 +1510,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-15.50254137</t>
+          <t>-15.48412238</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-70.12819875</t>
+          <t>-70.15438435</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO EL PORVENIR</t>
+          <t>SANTA ADRIANA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>JOSE DOMINGO CHOQUEHUANCA NUMERO 431 DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JR PACHACAMAC S/N NUMERO S/N DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1572,27 +1572,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-15.4986309</t>
+          <t>-15.48702365</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-70.133861</t>
+          <t>-70.1464084</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO ODONTOLOGICO AMERICANO FILIAL JULIACA</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Jr.PIURA 482 PARQUE GRAU DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JR CULTURA 235 SANTA MARIA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28343</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-15.49711356</t>
+          <t>-15.49796756</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-70.13139107</t>
+          <t>-70.14355121</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>POLICLINICO SOLIDARIO REGIONAL</t>
+          <t>LOS CHOFERES</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BRACESCO NUMERO 335 DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JR ESPINAL S/N NUMERO S/N DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1671,7 +1671,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>35161</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1696,27 +1696,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-15.488648</t>
+          <t>-15.43152167</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-70.1247988</t>
+          <t>-70.29427167</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO SAN MARTIN DE PORRES DEL SUR E.I.R.L.</t>
+          <t>CHANOCAHUA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HUANCANE NUMERO 970 PISO 1 DEPARTAMENTO 1 INTERIOR 1 URBANIZACION TUPAC AMARU DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>OTROS CENTRO POBLADO CHANOCAHUA S/N NUMERO S/N DISTRITO LAMPA PROVINCIA LAMPA DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>36190</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1758,22 +1758,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-15.4924826</t>
+          <t>-15.47815406</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-70.1268977</t>
+          <t>-70.14710242</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>POLICLINICO NAZARET S.A.C.</t>
+          <t>SANTA CATALINA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SAN MARTIN NUMERO 717A PISO 1 URBANIZACION TUPAC AMARU DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>JR CONJDORCANQUI MZA V-4 DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18154</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,27 +1820,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-15.4996879</t>
+          <t>-15.49956615</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-70.129653</t>
+          <t>-70.12985587</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO DEL VALLE</t>
+          <t>CONO SUR</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Jr.BENIGNO BALLAN NRO 968 DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
+          <t>AVENIDA AV. MANUEL NUNEZ BUTRON 134 DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1849,626 +1849,6 @@
         </is>
       </c>
       <c r="L23" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>30248</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-15.48871055</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-70.12263098</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>POLICLINICO OXIMEDIC HEALTH SAC</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>MOQUEGUA NUMERO 1219 PISO 2 DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>29192</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-15.48900879</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-70.16628113</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>CLINICA TRAUMATOLOGICA Y DE ESPECIALIDADES MEDICAS E.I.R.L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>ANJOLLANI PISO 1 MANZANA B LOTE 2 URBANIZACION COLLASUYO PUNO DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>30223</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-15.4996879</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-70.129653</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO "SAN ISIDRO LABRADOR"</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>JUAN VELASCO ALVARADO CON ATAHUALLPA NUMERO S/N URBANIZACION SAN ISIDRO DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>26593</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-15.4996879</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-70.129653</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>POLICLINICO HOLY ROSE JR</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>AVENIDA HUANCANE NUMERO 1295 DISTRITO SAN MIGUEL PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>25661</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-15.499</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-70.1348</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO ESPECIALIZADO CECAN</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>PIURA NUMERO 566 PISO 1 URBANIZACION LA RINCONADA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>I-4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>26066</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-15.4866528</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-70.118969</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>PROMEDICAS  CENTRO DE CIRUGIA AMBULATORIA Y CIRUGIA CORTA ESTANCIA</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>SAN MARTIN NUMERO 640 URBANIZACION Zarumilla DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>I-4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>25602</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-15.4927349</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-70.1282025</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO DEL VALLE</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>RAMAN CASTILLA NUMERO 723 PISO 1 URBANIZACION TUPAC AMARU DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>28067</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-15.4996879</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-70.129653</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>CENTRO ODONTOLOGICO  BALNER ALVAREZ</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>CALLAO - ESQUINA HIPOLITO UNANUE NUMERO 501 PISO 1 URBANIZACION LA RINCONADA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>26891</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-15.4960612</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-70.1356</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>POLICLINICO PERUANO SUIZO CONSALUD</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>MANUEL PRADO NUMERO 528 PISO 1 URBANIZACION LA RINCONADA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>35102</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-15.4996879</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-70.129653</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>POLICLINICO DIVINA PROVIDENCIA</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>FRANCISCO BOLOGNESI NUMERO 755 PISO 1 URBANIZACION LA PAMPILLA DISTRITO JULIACA PROVINCIA SAN ROMAN DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
         <is>
           <t>211101</t>
         </is>

--- a/EstablecimientoSalud/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>9901</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-15.4955005</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>10236</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-15.4996879</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>29844</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-15.4996879</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>29841</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-15.47996082</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>27818</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-15.53120166</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>30223</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-15.4996879</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>3315</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-15.516739</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>3310</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-15.43903137</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>15422</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-15.47607025</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>3316</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-15.43264619</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>3302</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-15.50102712</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>10887</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-15.49997221</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>18979</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-15.4996879</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>3308</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-15.48032349</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>10888</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-15.4955688</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>3307</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-15.4753026</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>3301</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-15.48412238</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>3314</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-15.48702365</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>3306</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-15.49796756</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>3129</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-15.43152167</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>3313</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-15.47815406</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>211101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SAN_ROMAN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>JULIACA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>3300</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-15.49956615</t>
@@ -1846,11 +1736,6 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>211101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/EstablecimientoSalud/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
